--- a/artfynd/A 31572-2023 artfynd.xlsx
+++ b/artfynd/A 31572-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31572-2023 artfynd.xlsx
+++ b/artfynd/A 31572-2023 artfynd.xlsx
@@ -675,51 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110947080</v>
+        <v>110947351</v>
       </c>
       <c r="B2" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>614510.1279625499</v>
+        <v>614545</v>
       </c>
       <c r="R2" t="n">
-        <v>6657642.00361704</v>
+        <v>6657690</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,7 +746,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +756,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,51 +783,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110947619</v>
+        <v>110948236</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>614481.0570550568</v>
+        <v>614412</v>
       </c>
       <c r="R3" t="n">
-        <v>6657755.583492418</v>
+        <v>6657797</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,7 +854,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +864,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110947019</v>
+        <v>110947380</v>
       </c>
       <c r="B4" t="n">
-        <v>103288</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,35 +902,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>614534.747918217</v>
+        <v>614570</v>
       </c>
       <c r="R4" t="n">
-        <v>6657623.271711768</v>
+        <v>6657699</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,7 +962,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +972,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,15 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110947410</v>
+        <v>110947035</v>
       </c>
       <c r="B5" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,14 +1031,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>614542.6751059515</v>
+        <v>614524</v>
       </c>
       <c r="R5" t="n">
-        <v>6657706.507382731</v>
+        <v>6657630</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1090,7 +1070,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1100,7 +1080,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,51 +1107,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110947351</v>
+        <v>110947080</v>
       </c>
       <c r="B6" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>614544.7041997212</v>
+        <v>614510</v>
       </c>
       <c r="R6" t="n">
-        <v>6657689.572886499</v>
+        <v>6657643</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,15 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110948255</v>
+        <v>110947410</v>
       </c>
       <c r="B7" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,14 +1247,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>614423.4236839975</v>
+        <v>614543</v>
       </c>
       <c r="R7" t="n">
-        <v>6657789.286310961</v>
+        <v>6657707</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1316,7 +1286,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1326,7 +1296,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,51 +1323,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110948236</v>
+        <v>110947491</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>614411.6690967374</v>
+        <v>614553</v>
       </c>
       <c r="R8" t="n">
-        <v>6657796.919702402</v>
+        <v>6657734</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1429,7 +1394,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1404,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1431,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110947035</v>
+        <v>110947619</v>
       </c>
       <c r="B9" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,14 +1463,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>614524.5089896603</v>
+        <v>614481</v>
       </c>
       <c r="R9" t="n">
-        <v>6657630.452345544</v>
+        <v>6657756</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1542,7 +1502,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1512,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>110947491</v>
+        <v>110948255</v>
       </c>
       <c r="B10" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,14 +1571,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>614553.3115441641</v>
+        <v>614424</v>
       </c>
       <c r="R10" t="n">
-        <v>6657734.834170708</v>
+        <v>6657789</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1655,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1665,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,12 +1650,7 @@
         <v>110948416</v>
       </c>
       <c r="B11" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1729,14 +1679,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>614392.0112977019</v>
+        <v>614392</v>
       </c>
       <c r="R11" t="n">
-        <v>6657768.813506908</v>
+        <v>6657768</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,12 +1758,7 @@
         <v>110948582</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,14 +1787,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bredmossen (Bredmossen), Upl</t>
+          <t>Bredmossen, Bredmossen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>614461.1684684249</v>
+        <v>614462</v>
       </c>
       <c r="R12" t="n">
-        <v>6657815.455187102</v>
+        <v>6657816</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1918,54 +1863,60 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110947380</v>
+        <v>110959452</v>
       </c>
       <c r="B13" t="n">
-        <v>96265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Björkmossen (Björkmossen), Upl</t>
+          <t>Sydväst om Råksjön, Öster om Huddungeby, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>614569.4543792737</v>
+        <v>614391</v>
       </c>
       <c r="R13" t="n">
-        <v>6657698.841700966</v>
+        <v>6657781</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1992,19 +1943,14 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:25</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:25</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Väldigt fin skog i området 60.03276 - 60.041821 N, 17.053614 - 17.077475 E</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2013,83 +1959,68 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Eric Grund</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>110959452</v>
+        <v>110947019</v>
       </c>
       <c r="B14" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sydväst om Råksjön, Öster om Huddungeby, Upl</t>
+          <t>Björkmossen, Björkmossen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>614390.6073367225</v>
+        <v>614535</v>
       </c>
       <c r="R14" t="n">
-        <v>6657781.76775714</v>
+        <v>6657624</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2118,7 +2049,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,12 +2059,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Väldigt fin skog i området 60.03276 - 60.041821 N, 17.053614 - 17.077475 E</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2142,19 +2068,18 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eric Grund</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 31572-2023 artfynd.xlsx
+++ b/artfynd/A 31572-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947351</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110948236</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947380</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947035</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947080</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947410</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1428,6 +1463,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947491</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947619</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110948255</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110948416</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110948582</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1975,6 +2035,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110959452</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2083,8 +2148,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110947019</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>